--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1354</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1355</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,16 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,52 +219,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,25 +241,38 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -318,10 +285,42 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -340,8 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +386,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,19 +422,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +488,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,97 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -591,6 +582,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,17 +643,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,183 +668,168 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="7">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="9">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1355"/>
+  <dimension ref="A1:E1356"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19115,9 +19115,20 @@
         <v>48667</v>
       </c>
     </row>
+    <row r="1356" spans="1:3">
+      <c r="A1356" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1356">
+        <v>20653</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1354">
-    <sortState ref="A1:E1354">
+  <autoFilter ref="A1:E1355">
+    <sortState ref="A1:E1355">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1357</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -211,7 +211,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,10 +239,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -239,6 +255,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,8 +277,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,18 +317,17 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,54 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +428,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,11 +615,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,201 +668,168 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="9">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1357"/>
+  <dimension ref="A1:E1358"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19137,9 +19137,20 @@
         <v>27478</v>
       </c>
     </row>
+    <row r="1358" spans="1:3">
+      <c r="A1358" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1358">
+        <v>34411</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1356">
-    <sortState ref="A1:E1356">
+  <autoFilter ref="A1:E1357">
+    <sortState ref="A1:E1357">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1357</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1358</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,15 +203,32 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,7 +243,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,36 +282,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,17 +297,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -300,24 +325,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -325,23 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +464,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,61 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,85 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,7 +590,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,17 +606,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,8 +628,19 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,162 +674,162 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1358"/>
+  <dimension ref="A1:E1359"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19148,9 +19148,20 @@
         <v>34411</v>
       </c>
     </row>
+    <row r="1359" spans="1:3">
+      <c r="A1359" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1359">
+        <v>63150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1357">
-    <sortState ref="A1:E1357">
+  <autoFilter ref="A1:E1358">
+    <sortState ref="A1:E1358">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1358</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1359</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,7 +205,45 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,23 +257,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -256,32 +309,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,14 +324,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -311,37 +332,16 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +476,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,37 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,91 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -589,38 +604,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,26 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,162 +674,162 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1359"/>
+  <dimension ref="A1:E1360"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19159,9 +19159,20 @@
         <v>63150</v>
       </c>
     </row>
+    <row r="1360" spans="1:3">
+      <c r="A1360" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1360">
+        <v>44081</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1358">
-    <sortState ref="A1:E1358">
+  <autoFilter ref="A1:E1359">
+    <sortState ref="A1:E1359">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1360</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,35 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -211,16 +240,69 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,43 +316,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -280,30 +325,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -319,29 +342,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +398,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +410,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +476,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,73 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,21 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,6 +619,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -634,11 +643,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,37 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
@@ -692,144 +692,144 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="9">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1360"/>
+  <dimension ref="A1:E1361"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19170,9 +19170,20 @@
         <v>44081</v>
       </c>
     </row>
+    <row r="1361" spans="1:3">
+      <c r="A1361" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1361">
+        <v>23982</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1359">
-    <sortState ref="A1:E1359">
+  <autoFilter ref="A1:E1360">
+    <sortState ref="A1:E1360">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1360</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1361</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,92 +217,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,7 +233,52 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -332,8 +293,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +335,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,31 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +398,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,25 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,13 +476,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +575,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,30 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,7 +614,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,6 +634,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -668,168 +659,177 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="3">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1361"/>
+  <dimension ref="A1:E1362"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19181,9 +19181,20 @@
         <v>23982</v>
       </c>
     </row>
+    <row r="1362" spans="1:3">
+      <c r="A1362" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1362">
+        <v>85567</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1360">
-    <sortState ref="A1:E1360">
+  <autoFilter ref="A1:E1361">
+    <sortState ref="A1:E1361">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1362</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,24 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,6 +228,37 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,6 +273,43 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -240,23 +324,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,76 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,163 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,21 +595,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -651,6 +636,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -660,11 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,162 +674,162 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1362"/>
+  <dimension ref="A1:E1363"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19192,9 +19192,20 @@
         <v>85567</v>
       </c>
     </row>
+    <row r="1363" spans="1:3">
+      <c r="A1363" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1363">
+        <v>14948</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1361">
-    <sortState ref="A1:E1361">
+  <autoFilter ref="A1:E1362">
+    <sortState ref="A1:E1362">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1362</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1363</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -212,7 +212,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,22 +234,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,16 +264,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,30 +333,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,21 +342,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,31 +440,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,79 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,6 +581,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -604,6 +619,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -619,30 +658,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -653,88 +668,73 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="3">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2">
@@ -743,93 +743,93 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="9">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1363"/>
+  <dimension ref="A1:E1364"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19203,9 +19203,20 @@
         <v>14948</v>
       </c>
     </row>
+    <row r="1364" spans="1:3">
+      <c r="A1364" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1364">
+        <v>34658</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1362">
-    <sortState ref="A1:E1362">
+  <autoFilter ref="A1:E1363">
+    <sortState ref="A1:E1363">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1364</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,31 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,15 +227,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,11 +241,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -281,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,7 +273,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,16 +293,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +333,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,6 +362,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,19 +428,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,115 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,24 +573,20 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,26 +606,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +647,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="8">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1364"/>
+  <dimension ref="A1:E1365"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19214,9 +19214,20 @@
         <v>34658</v>
       </c>
     </row>
+    <row r="1365" spans="1:3">
+      <c r="A1365" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1365">
+        <v>87707</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1363">
-    <sortState ref="A1:E1363">
+  <autoFilter ref="A1:E1364">
+    <sortState ref="A1:E1364">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1364</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1365</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,23 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,23 +212,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,6 +235,43 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -265,7 +279,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,13 +294,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -294,9 +301,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -309,25 +324,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -341,7 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +422,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,13 +458,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,25 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,22 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,15 +616,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -648,23 +634,37 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="4">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="9">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1365"/>
+  <dimension ref="A1:E1366"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19225,9 +19225,20 @@
         <v>87707</v>
       </c>
     </row>
+    <row r="1366" spans="1:3">
+      <c r="A1366" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1366">
+        <v>15984</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1364">
-    <sortState ref="A1:E1364">
+  <autoFilter ref="A1:E1365">
+    <sortState ref="A1:E1365">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1365</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1366</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,32 +203,25 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,8 +241,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,23 +271,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,7 +295,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,22 +326,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -339,9 +333,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,61 +464,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,43 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,25 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,6 +621,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -631,20 +645,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,24 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
@@ -683,153 +683,153 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1366"/>
+  <dimension ref="A1:E1367"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19236,9 +19236,20 @@
         <v>15984</v>
       </c>
     </row>
+    <row r="1367" spans="1:3">
+      <c r="A1367" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1367">
+        <v>39728</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1365">
-    <sortState ref="A1:E1365">
+  <autoFilter ref="A1:E1366">
+    <sortState ref="A1:E1366">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1367</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,25 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,37 +218,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,7 +248,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,6 +272,36 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,10 +316,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -327,21 +333,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +386,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,67 +488,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,26 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,6 +610,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -645,17 +640,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +653,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
@@ -695,141 +695,141 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="7">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="4">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1367"/>
+  <dimension ref="A1:E1368"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19247,9 +19247,20 @@
         <v>39728</v>
       </c>
     </row>
+    <row r="1368" spans="1:3">
+      <c r="A1368" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1368">
+        <v>14858</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1366">
-    <sortState ref="A1:E1366">
+  <autoFilter ref="A1:E1367">
+    <sortState ref="A1:E1367">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1367</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1368</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,59 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,14 +226,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,6 +257,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,11 +285,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -333,15 +327,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,85 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,13 +470,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -603,6 +603,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -644,7 +655,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,18 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,162 +674,162 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="2">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="6">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1368"/>
+  <dimension ref="A1:E1369"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19258,9 +19258,20 @@
         <v>14858</v>
       </c>
     </row>
+    <row r="1369" spans="1:3">
+      <c r="A1369" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1369">
+        <v>25390</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1367">
-    <sortState ref="A1:E1367">
+  <autoFilter ref="A1:E1368">
+    <sortState ref="A1:E1368">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1369</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,22 +241,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,22 +256,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,6 +270,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -294,7 +293,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -306,14 +305,6 @@
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -333,15 +324,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,6 +362,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,7 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +398,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,61 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -621,17 +621,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,16 +649,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,162 +674,162 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="2">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1369"/>
+  <dimension ref="A1:E1370"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19269,9 +19269,17 @@
         <v>25390</v>
       </c>
     </row>
+    <row r="1370" spans="1:2">
+      <c r="A1370" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1368">
-    <sortState ref="A1:E1368">
+  <autoFilter ref="A1:E1369">
+    <sortState ref="A1:E1369">
       <sortCondition ref="A2:A1354"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1370</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1371</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,6 +210,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -224,17 +240,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,8 +277,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,14 +287,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,46 +327,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,7 +368,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,25 +440,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,19 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,56 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -638,9 +588,59 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,67 +674,67 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -743,89 +743,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1371"/>
+  <dimension ref="A1:E1372"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19289,8 +19289,19 @@
         <v>654541</v>
       </c>
     </row>
+    <row r="1372" spans="1:3">
+      <c r="A1372" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1372">
+        <v>190932</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1370">
+  <autoFilter ref="A1:E1371">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1371</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1372</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -212,14 +212,76 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,7 +303,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,9 +332,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,83 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,7 +368,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +392,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,145 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,16 +571,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -588,11 +588,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,17 +621,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -645,26 +645,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,142 +674,142 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1372"/>
+  <dimension ref="A1:E1373"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19300,8 +19300,19 @@
         <v>190932</v>
       </c>
     </row>
+    <row r="1373" spans="1:3">
+      <c r="A1373" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1373">
+        <v>276985</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1371">
+  <autoFilter ref="A1:E1372">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1373</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,16 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,77 +219,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,8 +248,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,8 +310,31 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,37 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,35 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,17 +595,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -641,15 +606,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +624,208 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1373"/>
+  <dimension ref="A1:E1374"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19311,8 +19311,19 @@
         <v>276985</v>
       </c>
     </row>
+    <row r="1374" spans="1:3">
+      <c r="A1374" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1374">
+        <v>178624</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1372">
+  <autoFilter ref="A1:E1373">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1374</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,15 +219,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,11 +256,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -264,31 +279,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,10 +294,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -318,7 +318,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,7 +326,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +428,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,19 +482,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,55 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,47 +634,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -647,8 +645,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1374"/>
+  <dimension ref="A1:E1375"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19322,8 +19322,19 @@
         <v>178624</v>
       </c>
     </row>
+    <row r="1375" spans="1:3">
+      <c r="A1375" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1375">
+        <v>218061</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1373">
+  <autoFilter ref="A1:E1374">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1374</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1375</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,15 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,40 +225,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -265,39 +250,9 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,6 +272,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -332,9 +324,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +334,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +434,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,39 +628,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -650,6 +641,15 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1375"/>
+  <dimension ref="A1:E1376"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19333,8 +19333,19 @@
         <v>218061</v>
       </c>
     </row>
+    <row r="1376" spans="1:3">
+      <c r="A1376" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1376">
+        <v>228800</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1374">
+  <autoFilter ref="A1:E1375">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1376</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,59 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -281,7 +228,59 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,7 +294,23 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -316,14 +331,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -332,18 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +386,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,31 +506,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,6 +582,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,29 +627,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +650,182 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1376"/>
+  <dimension ref="A1:E1377"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19344,8 +19344,19 @@
         <v>228800</v>
       </c>
     </row>
+    <row r="1377" spans="1:3">
+      <c r="A1377" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1377">
+        <v>207404</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1375">
+  <autoFilter ref="A1:E1376">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1376</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1377</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,10 +204,32 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -219,24 +241,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,44 +257,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,14 +280,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -324,13 +309,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -339,11 +317,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +374,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,55 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +434,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,49 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -588,8 +597,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -627,11 +638,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,40 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1377"/>
+  <dimension ref="A1:E1378"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19355,8 +19355,19 @@
         <v>207404</v>
       </c>
     </row>
+    <row r="1378" spans="1:3">
+      <c r="A1378" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1378">
+        <v>278960</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1376">
+  <autoFilter ref="A1:E1377">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1377</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1378</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,23 +203,24 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,9 +228,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -256,20 +278,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,7 +288,44 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,55 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +422,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,17 +601,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -617,21 +612,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,7 +629,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,13 +659,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1378"/>
+  <dimension ref="A1:E1379"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19366,8 +19366,19 @@
         <v>278960</v>
       </c>
     </row>
+    <row r="1379" spans="1:3">
+      <c r="A1379" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1379">
+        <v>310045</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1377">
+  <autoFilter ref="A1:E1378">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1378</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1379</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,23 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,44 +212,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,17 +225,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,8 +254,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,14 +271,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,11 +293,57 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,121 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,21 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,6 +604,30 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -629,17 +638,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -662,9 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1379"/>
+  <dimension ref="A1:E1380"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19377,8 +19377,19 @@
         <v>310045</v>
       </c>
     </row>
+    <row r="1380" spans="1:3">
+      <c r="A1380" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1380">
+        <v>10612</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1378">
+  <autoFilter ref="A1:E1379">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1380</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -204,35 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -254,6 +225,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -262,9 +247,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,14 +264,6 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -294,14 +271,61 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,34 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,103 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,6 +380,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -488,7 +404,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,31 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +494,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,43 +610,27 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -660,11 +653,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1380"/>
+  <dimension ref="A1:E1381"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19388,8 +19388,19 @@
         <v>10612</v>
       </c>
     </row>
+    <row r="1381" spans="1:3">
+      <c r="A1381" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1381">
+        <v>53331</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1379">
+  <autoFilter ref="A1:E1380">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1380</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1381</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,12 +204,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -219,6 +220,97 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -241,101 +333,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,13 +362,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,133 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +458,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +488,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,9 +573,65 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,67 +651,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,67 +674,67 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -743,89 +743,89 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1381"/>
+  <dimension ref="A1:E1382"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19399,8 +19399,19 @@
         <v>53331</v>
       </c>
     </row>
+    <row r="1382" spans="1:3">
+      <c r="A1382" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1382">
+        <v>67683</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1380">
+  <autoFilter ref="A1:E1381">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1381</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1382</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,39 +258,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -259,6 +275,43 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,47 +326,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -321,29 +344,6 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +410,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,19 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,13 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,61 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +500,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,69 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,71 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1382"/>
+  <dimension ref="A1:E1383"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19410,8 +19410,19 @@
         <v>67683</v>
       </c>
     </row>
+    <row r="1383" spans="1:3">
+      <c r="A1383" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1383">
+        <v>67683</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1381">
+  <autoFilter ref="A1:E1382">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1382</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1383</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,40 +210,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,6 +226,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -265,9 +249,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,14 +286,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,21 +333,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -325,21 +340,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -362,7 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,79 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,37 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +506,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,26 +591,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,35 +632,39 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1383"/>
+  <dimension ref="A1:E1384"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19421,8 +19421,19 @@
         <v>67683</v>
       </c>
     </row>
+    <row r="1384" spans="1:3">
+      <c r="A1384" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1384">
+        <v>62998</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1382">
+  <autoFilter ref="A1:E1383">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1384</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -219,47 +219,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,22 +241,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,9 +278,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,25 +332,18 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +434,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,55 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,35 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -611,6 +582,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,8 +622,34 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,28 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1384"/>
+  <dimension ref="A1:E1385"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19432,8 +19432,19 @@
         <v>62998</v>
       </c>
     </row>
+    <row r="1385" spans="1:3">
+      <c r="A1385" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1385">
+        <v>64829</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1383">
+  <autoFilter ref="A1:E1384">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1384</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1385</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -204,67 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,17 +232,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -315,9 +286,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +326,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +488,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,132 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,25 +572,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,16 +596,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +659,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1385"/>
+  <dimension ref="A1:E1386"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19443,8 +19443,19 @@
         <v>64829</v>
       </c>
     </row>
+    <row r="1386" spans="1:3">
+      <c r="A1386" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1386">
+        <v>103713</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1384">
+  <autoFilter ref="A1:E1385">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1385</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1386</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -167,8 +167,8 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,8 +210,91 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,8 +308,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,95 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,25 +368,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,6 +392,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -416,25 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,19 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,31 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,13 +506,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,31 +590,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,21 +602,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +625,46 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1386"/>
+  <dimension ref="A1:E1387"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19454,8 +19454,19 @@
         <v>103713</v>
       </c>
     </row>
+    <row r="1387" spans="1:3">
+      <c r="A1387" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1387">
+        <v>84920</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1385">
+  <autoFilter ref="A1:E1386">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1386</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1388</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,23 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,7 +218,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,38 +250,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -293,8 +272,15 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,22 +296,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -333,17 +303,47 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,37 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,121 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,15 +588,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -606,17 +597,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,8 +609,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +645,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1387"/>
+  <dimension ref="A1:E1389"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19465,8 +19465,30 @@
         <v>84920</v>
       </c>
     </row>
+    <row r="1388" spans="1:3">
+      <c r="A1388" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1388">
+        <v>84920</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:3">
+      <c r="A1389" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1389">
+        <v>69542</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1386">
+  <autoFilter ref="A1:E1388">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1388</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1389</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,8 +164,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
@@ -210,15 +210,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,14 +242,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -250,17 +252,32 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -280,30 +297,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,14 +319,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +342,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,49 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +434,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +470,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,16 +610,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,26 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1389"/>
+  <dimension ref="A1:E1390"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19487,8 +19487,19 @@
         <v>69542</v>
       </c>
     </row>
+    <row r="1390" spans="1:3">
+      <c r="A1390" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1390">
+        <v>71796</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1388">
+  <autoFilter ref="A1:E1389">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1389</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1390</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,11 +246,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -251,15 +294,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,16 +316,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,57 +344,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,43 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +380,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,13 +470,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,37 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -582,6 +591,21 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,16 +640,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,188 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1390"/>
+  <dimension ref="A1:E1391"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19498,8 +19498,19 @@
         <v>71796</v>
       </c>
     </row>
+    <row r="1391" spans="1:3">
+      <c r="A1391" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1391">
+        <v>48539</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1389">
+  <autoFilter ref="A1:E1390">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1391</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,41 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -261,15 +226,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -277,17 +247,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,6 +266,14 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -316,8 +292,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,7 +332,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,42 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -410,19 +374,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +410,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,31 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,37 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,15 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,8 +624,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +659,173 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1391"/>
+  <dimension ref="A1:E1392"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19509,8 +19509,19 @@
         <v>48539</v>
       </c>
     </row>
+    <row r="1392" spans="1:3">
+      <c r="A1392" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1392">
+        <v>72098</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1390">
+  <autoFilter ref="A1:E1391">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1392</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -205,16 +205,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,8 +219,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,15 +248,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,16 +295,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,7 +305,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,50 +319,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,7 +368,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +446,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,55 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,61 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -582,41 +591,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,6 +620,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -656,6 +645,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1392"/>
+  <dimension ref="A1:E1393"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19520,8 +19520,19 @@
         <v>72098</v>
       </c>
     </row>
+    <row r="1393" spans="1:3">
+      <c r="A1393" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1393">
+        <v>68367</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1391">
+  <autoFilter ref="A1:E1392">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1393</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,19 +203,10 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -228,7 +219,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,15 +255,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,15 +269,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -280,15 +308,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -303,9 +323,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,35 +333,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,6 +362,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,7 +380,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +410,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,49 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -591,15 +582,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,6 +601,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -630,6 +621,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -651,17 +662,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1393"/>
+  <dimension ref="A1:E1394"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19531,8 +19531,19 @@
         <v>68367</v>
       </c>
     </row>
+    <row r="1394" spans="1:3">
+      <c r="A1394" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1394">
+        <v>98601</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1392">
+  <autoFilter ref="A1:E1393">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1394</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,66 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -212,7 +272,31 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,36 +318,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,22 +326,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,50 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,61 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,49 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,19 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -601,11 +586,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,22 +639,22 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -663,8 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1394"/>
+  <dimension ref="A1:E1395"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19542,8 +19542,19 @@
         <v>98601</v>
       </c>
     </row>
+    <row r="1395" spans="1:3">
+      <c r="A1395" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1395">
+        <v>72517</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1393">
+  <autoFilter ref="A1:E1394">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1394</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1396</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,23 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,16 +219,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,8 +248,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,7 +258,52 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,14 +325,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -310,40 +333,17 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,169 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -582,6 +597,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,23 +652,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,55 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1395"/>
+  <dimension ref="A1:E1397"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19553,8 +19553,30 @@
         <v>72517</v>
       </c>
     </row>
+    <row r="1396" spans="1:3">
+      <c r="A1396" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1396">
+        <v>72517</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:3">
+      <c r="A1397" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1397">
+        <v>23092</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1394">
+  <autoFilter ref="A1:E1396">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1396</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1397</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,130 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,128 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,25 +398,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +416,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,13 +452,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,37 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,59 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -602,39 +655,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -648,184 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1397"/>
+  <dimension ref="A1:E1398"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19575,8 +19575,19 @@
         <v>23092</v>
       </c>
     </row>
+    <row r="1398" spans="1:3">
+      <c r="A1398" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1398">
+        <v>100316</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1396">
+  <autoFilter ref="A1:E1397">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1397</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1398</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,7 +204,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,8 +254,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,16 +315,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,14 +333,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,61 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +410,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,97 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,27 +573,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,10 +614,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -639,17 +636,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1398"/>
+  <dimension ref="A1:E1399"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19586,8 +19586,19 @@
         <v>100316</v>
       </c>
     </row>
+    <row r="1399" spans="1:3">
+      <c r="A1399" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1399">
+        <v>35281</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1397">
+  <autoFilter ref="A1:E1398">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1398</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1399</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,8 +164,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
@@ -204,7 +204,50 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,28 +262,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,22 +276,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -278,16 +284,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,23 +315,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,19 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +428,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,31 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,91 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,26 +573,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -608,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,9 +612,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,8 +624,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1399"/>
+  <dimension ref="A1:E1400"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19597,8 +19597,19 @@
         <v>35281</v>
       </c>
     </row>
+    <row r="1400" spans="1:3">
+      <c r="A1400" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1400">
+        <v>22335</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1398">
+  <autoFilter ref="A1:E1399">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1399</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1400</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -211,7 +211,53 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,8 +270,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,25 +286,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -265,14 +306,6 @@
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -284,24 +317,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -315,31 +333,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -362,7 +362,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +452,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,79 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,6 +582,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,22 +621,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1400"/>
+  <dimension ref="A1:E1401"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19608,8 +19608,19 @@
         <v>22335</v>
       </c>
     </row>
+    <row r="1401" spans="1:3">
+      <c r="A1401" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1401">
+        <v>55281</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1399">
+  <autoFilter ref="A1:E1400">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1400</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1401</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -203,6 +203,59 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -210,8 +263,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,17 +288,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -247,32 +302,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,37 +324,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -325,25 +332,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,31 +488,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,73 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -588,50 +597,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,8 +624,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +648,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1401"/>
+  <dimension ref="A1:E1402"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19619,8 +19619,19 @@
         <v>55281</v>
       </c>
     </row>
+    <row r="1402" spans="1:3">
+      <c r="A1402" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1402">
+        <v>35806</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1400">
+  <autoFilter ref="A1:E1401">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Qoo10.xlsx
+++ b/dashboard/data/incoming/Qoo10.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1402</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,6 +203,43 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -211,11 +248,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -235,42 +309,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -279,24 +317,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,41 +332,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,6 +362,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,49 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +458,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,31 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,25 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,13 +518,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -607,16 +598,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +645,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1402"/>
+  <dimension ref="A1:E1403"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -19630,8 +19630,19 @@
         <v>35806</v>
       </c>
     </row>
+    <row r="1403" spans="1:3">
+      <c r="A1403" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1403">
+        <v>34225</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1401">
+  <autoFilter ref="A1:E1402">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
